--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/biobio.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1986,7 +1986,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4988-39-CM25</t>
+          <t>4359-202-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2026,32 +2026,28 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>230449.24</v>
+        <v>34461.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4359-202-CM25</t>
+          <t>4988-39-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2071,17 +2067,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2091,22 +2087,26 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>34461.19</v>
+        <v>230449.24</v>
       </c>
     </row>
     <row r="28">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1347776-13-CM25</t>
+          <t>995118-180-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>61220.05</v>
+        <v>50233.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>995118-180-CM25</t>
+          <t>3319-249-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>50233.74</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3319-249-CM25</t>
+          <t>998-290-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3128,28 +3128,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Janssen S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>81.198.100-1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>42056.86</v>
+        <v>113953.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>998-290-CM25</t>
+          <t>1208129-774-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3164,7 +3168,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3174,12 +3178,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3189,32 +3193,28 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Janssen S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>81.198.100-1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>113953.77</v>
+        <v>17484.18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1208129-774-CM25</t>
+          <t>4414-1824-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3234,17 +3234,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>17484.18</v>
+        <v>75574.33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4414-1824-CM25</t>
+          <t>1375757-103-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3290,22 +3290,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>75574.33</v>
+        <v>25952.33</v>
       </c>
     </row>
     <row r="48">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Tattersall Maquinarias S.A.</t>
+          <t>TATTERSALL MAQUINARIAS S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3462,7 +3462,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>654-33-CM26</t>
+          <t>1456839-3-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.981.420-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>27247.95</v>
+        <v>27869.69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2410-5-CM26</t>
+          <t>654-33-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3563,32 +3563,28 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>63506.13</v>
+        <v>27247.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3945-128-CM26</t>
+          <t>2410-5-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3598,12 +3594,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3613,12 +3609,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3628,22 +3624,26 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>23363.4</v>
+        <v>63506.13</v>
       </c>
     </row>
     <row r="53">
@@ -3710,7 +3710,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1456840-10-CM26</t>
+          <t>3945-128-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>24347.42</v>
+        <v>23363.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4988-6-CM26</t>
+          <t>3577-31-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.929.100-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3811,32 +3811,28 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Guillermo Morales Ltda</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.564.810-0</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>104460.72</v>
+        <v>18749.18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4362-22-CM26</t>
+          <t>4988-6-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3851,7 +3847,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3861,12 +3857,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3876,58 +3872,62 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Guillermo Morales Ltda</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>96.564.810-0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>24750.82</v>
+        <v>104460.72</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1208910-77-CM26</t>
+          <t>4362-22-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>65.201.852-1</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>39506.9</v>
+        <v>24750.82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1079650-31-CM26</t>
+          <t>1208910-77-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3968,27 +3968,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>65.201.852-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>79052.75</v>
+        <v>39506.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3977-52-CM26</t>
+          <t>3567-278-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.170.202-2</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4074,13 +4074,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>34406.67</v>
+        <v>39491.98</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4414-752-CM26</t>
+          <t>1079650-31-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4135,13 +4135,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>53773.91</v>
+        <v>79052.75</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4034-309-CM26</t>
+          <t>3977-52-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>69.170.202-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4181,32 +4181,28 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>108064.84</v>
+        <v>34406.67</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3801-36-CM26</t>
+          <t>3567-317-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4216,12 +4212,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4231,12 +4227,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>69.150.700-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4246,12 +4242,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AUTO SUMMIT CHILE S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.924.460-8</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4261,13 +4257,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>48454.56</v>
+        <v>77801.52</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4236-511-CM26</t>
+          <t>4414-752-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4277,12 +4273,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4292,12 +4288,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4307,12 +4303,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4322,13 +4318,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>37822.07</v>
+        <v>53773.91</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4083-352-CM26</t>
+          <t>4034-309-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4343,7 +4339,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4353,12 +4349,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4368,28 +4364,32 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>37371.82</v>
+        <v>108064.84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4494-544-CM26</t>
+          <t>3801-36-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4404,22 +4404,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.172.600-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTO SUMMIT CHILE S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>96.924.460-8</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4444,13 +4444,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>34203.75</v>
+        <v>48454.56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4494-590-CM26</t>
+          <t>4236-511-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>FK SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.050.575-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1092.05</v>
+        <v>37822.07</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4494-589-CM26</t>
+          <t>4083-352-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FK SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.050.575-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4566,13 +4566,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>16391.94</v>
+        <v>37371.82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2416-201-CM26</t>
+          <t>4494-544-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4627,7 +4627,495 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
+        <v>34203.75</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4494-589-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>69.150.500-6</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PENCO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>FK SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.050.575-5</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>16391.94</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4494-590-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.150.500-6</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PENCO</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>FK SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>77.050.575-5</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>1092.05</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2416-201-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
         <v>42840</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4858-804-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.160.700-3</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>34871.35</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4858-828-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>69.160.700-3</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>34742.03</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4486-282-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>69.170.800-4</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>69425.91</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>654-325-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.820.004-3</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>25882.07</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>654-326-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.820.004-3</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>411.49</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/biobio.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/biobio.xlsx
@@ -562,7 +562,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1851,7 +1919,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1912,7 +1984,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1973,7 +2049,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2034,7 +2114,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2160,7 +2244,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2221,7 +2309,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2282,7 +2374,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2343,7 +2439,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2404,7 +2504,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2465,7 +2569,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2526,7 +2634,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2587,7 +2699,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2648,7 +2764,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2709,7 +2829,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2770,7 +2894,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2831,7 +2959,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2892,7 +3024,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2953,7 +3089,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3014,7 +3154,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3075,7 +3219,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3201,7 +3349,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3262,7 +3414,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3323,7 +3479,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3449,7 +3609,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3510,7 +3674,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3571,7 +3739,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3697,7 +3869,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3758,7 +3934,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3819,7 +3999,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3945,7 +4129,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4006,7 +4194,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4067,7 +4259,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4128,7 +4324,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4250,7 +4450,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4311,7 +4515,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4498,7 +4706,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4559,7 +4771,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4620,7 +4836,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4681,7 +4901,11 @@
           <t>77.050.575-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4742,7 +4966,11 @@
           <t>77.050.575-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4803,7 +5031,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4864,7 +5096,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4925,7 +5161,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4986,7 +5226,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5047,7 +5291,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5108,7 +5356,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/biobio.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2066,7 +2066,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4359-202-CM25</t>
+          <t>4988-39-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>34461.19</v>
+        <v>230449.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4988-39-CM25</t>
+          <t>4359-202-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>230449.24</v>
+        <v>34461.19</v>
       </c>
     </row>
     <row r="28">
@@ -3821,7 +3821,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2704-200-CM26</t>
+          <t>3945-128-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3880,13 +3880,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>10683.79</v>
+        <v>23363.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3945-128-CM26</t>
+          <t>2704-200-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>23363.4</v>
+        <v>10683.79</v>
       </c>
     </row>
     <row r="55">
@@ -4853,7 +4853,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4494-589-CM26</t>
+          <t>4494-590-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4912,13 +4912,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>16391.94</v>
+        <v>1092.05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4494-590-CM26</t>
+          <t>4494-589-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1092.05</v>
+        <v>16391.94</v>
       </c>
     </row>
     <row r="71">
@@ -5243,7 +5243,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>654-325-CM26</t>
+          <t>654-326-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5302,13 +5302,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>25882.07</v>
+        <v>411.49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>654-326-CM26</t>
+          <t>654-325-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5367,7 +5367,202 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>411.49</v>
+        <v>25882.07</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4988-90-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>360459.05</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4075-202-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>69.150.901-K</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>35950.91</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4988-116-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.150.400-K</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>EPYSA BUSES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>77.824.870-0</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>544269.13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/biobio.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/biobio.xlsx
@@ -4487,7 +4487,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
